--- a/artfynd/A 902-2023 artfynd.xlsx
+++ b/artfynd/A 902-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>115413237</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -790,12 +785,7 @@
         <v>115413232</v>
       </c>
       <c r="B3" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115413224</v>
+        <v>115413233</v>
       </c>
       <c r="B4" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,43 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gråliden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>752306</v>
+        <v>752266</v>
       </c>
       <c r="R4" t="n">
-        <v>7217238</v>
+        <v>7217100</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,15 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115413225</v>
+        <v>115413224</v>
       </c>
       <c r="B5" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,7 +1043,7 @@
         <v>752306</v>
       </c>
       <c r="R5" t="n">
-        <v>7217202</v>
+        <v>7217238</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1141,15 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115413226</v>
+        <v>115413225</v>
       </c>
       <c r="B6" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1190,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>752294</v>
+        <v>752306</v>
       </c>
       <c r="R6" t="n">
-        <v>7217172</v>
+        <v>7217202</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1225,7 +1191,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1235,7 +1201,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,15 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115413233</v>
+        <v>115413226</v>
       </c>
       <c r="B7" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,34 +1239,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gråliden, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>752266</v>
+        <v>752294</v>
       </c>
       <c r="R7" t="n">
-        <v>7217100</v>
+        <v>7217172</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1337,7 +1307,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1317,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,50 +1344,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115413235</v>
+        <v>115413231</v>
       </c>
       <c r="B8" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>102613</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gråliden, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>752262</v>
+        <v>752178</v>
       </c>
       <c r="R8" t="n">
-        <v>7217078</v>
+        <v>7216950</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1449,7 +1423,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1433,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,127 +1457,6 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>115413231</v>
-      </c>
-      <c r="B9" t="n">
-        <v>56481</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>102613</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Orre</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Lyrurus tetrix</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Gråliden, Vb</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>752178</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7216950</v>
-      </c>
-      <c r="S9" t="n">
-        <v>25</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Jörn</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2024-03-19</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-03-19</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:42</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
